--- a/data/nzd0063/nzd0063.xlsx
+++ b/data/nzd0063/nzd0063.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q341"/>
+  <dimension ref="A1:Q342"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19887,6 +19887,63 @@
         <v>363.49</v>
       </c>
       <c r="Q341" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:11:45+00:00</t>
+        </is>
+      </c>
+      <c r="B342" t="n">
+        <v>355.98</v>
+      </c>
+      <c r="C342" t="n">
+        <v>343.17</v>
+      </c>
+      <c r="D342" t="n">
+        <v>350.89</v>
+      </c>
+      <c r="E342" t="n">
+        <v>359.24</v>
+      </c>
+      <c r="F342" t="n">
+        <v>363.37</v>
+      </c>
+      <c r="G342" t="n">
+        <v>362.16</v>
+      </c>
+      <c r="H342" t="n">
+        <v>355.62</v>
+      </c>
+      <c r="I342" t="n">
+        <v>356.92</v>
+      </c>
+      <c r="J342" t="n">
+        <v>351.69</v>
+      </c>
+      <c r="K342" t="n">
+        <v>356.57</v>
+      </c>
+      <c r="L342" t="n">
+        <v>359.32</v>
+      </c>
+      <c r="M342" t="n">
+        <v>357.37</v>
+      </c>
+      <c r="N342" t="n">
+        <v>358.3</v>
+      </c>
+      <c r="O342" t="n">
+        <v>364.44</v>
+      </c>
+      <c r="P342" t="n">
+        <v>363.03</v>
+      </c>
+      <c r="Q342" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -19903,7 +19960,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B348"/>
+  <dimension ref="A1:B349"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23386,6 +23443,16 @@
       </c>
       <c r="B348" t="n">
         <v>0.23</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B349" t="n">
+        <v>1.14</v>
       </c>
     </row>
   </sheetData>
@@ -23554,28 +23621,28 @@
         <v>0.0544</v>
       </c>
       <c r="I2" t="n">
-        <v>0.04919802261677308</v>
+        <v>0.04914945344893933</v>
       </c>
       <c r="J2" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="K2" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="L2" t="n">
-        <v>0.009278299862632178</v>
+        <v>0.009323211074263926</v>
       </c>
       <c r="M2" t="n">
-        <v>2.915560979572826</v>
+        <v>2.907240817367021</v>
       </c>
       <c r="N2" t="n">
-        <v>13.924027727518</v>
+        <v>13.88321336145493</v>
       </c>
       <c r="O2" t="n">
-        <v>3.731491354340513</v>
+        <v>3.72601843278518</v>
       </c>
       <c r="P2" t="n">
-        <v>354.7688549547154</v>
+        <v>354.7693528568586</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -23636,28 +23703,28 @@
         <v>0.06</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.02690675743431567</v>
+        <v>-0.02715801826354193</v>
       </c>
       <c r="J3" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="K3" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003985563339625631</v>
+        <v>0.004087631417205251</v>
       </c>
       <c r="M3" t="n">
-        <v>2.26756442886962</v>
+        <v>2.262168622277435</v>
       </c>
       <c r="N3" t="n">
-        <v>9.747314018324998</v>
+        <v>9.719226228827383</v>
       </c>
       <c r="O3" t="n">
-        <v>3.1220688682867</v>
+        <v>3.117567357544562</v>
       </c>
       <c r="P3" t="n">
-        <v>344.2947745681624</v>
+        <v>344.2973503443375</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -23718,28 +23785,28 @@
         <v>0.06279999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>0.007146563043438088</v>
+        <v>0.006508551121326791</v>
       </c>
       <c r="J4" t="n">
+        <v>341</v>
+      </c>
+      <c r="K4" t="n">
         <v>340</v>
       </c>
-      <c r="K4" t="n">
-        <v>339</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.0002031716225635583</v>
+        <v>0.0001696372268977786</v>
       </c>
       <c r="M4" t="n">
-        <v>2.72817931620085</v>
+        <v>2.72343760436847</v>
       </c>
       <c r="N4" t="n">
-        <v>13.57604738640119</v>
+        <v>13.5393319390674</v>
       </c>
       <c r="O4" t="n">
-        <v>3.684568819604431</v>
+        <v>3.679583120282433</v>
       </c>
       <c r="P4" t="n">
-        <v>351.7486623180502</v>
+        <v>351.7551973373833</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -23800,28 +23867,28 @@
         <v>0.09859999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.02429950422304909</v>
+        <v>-0.02341618212342861</v>
       </c>
       <c r="J5" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="K5" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="L5" t="n">
-        <v>0.003438291430656215</v>
+        <v>0.00321338982426167</v>
       </c>
       <c r="M5" t="n">
-        <v>2.329002464457925</v>
+        <v>2.326231880058694</v>
       </c>
       <c r="N5" t="n">
-        <v>9.220248994238519</v>
+        <v>9.199349043193488</v>
       </c>
       <c r="O5" t="n">
-        <v>3.036486290803652</v>
+        <v>3.033042868670584</v>
       </c>
       <c r="P5" t="n">
-        <v>358.4267279722726</v>
+        <v>358.4176726809002</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -23882,28 +23949,28 @@
         <v>0.0949</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.06213080102009094</v>
+        <v>-0.06193490271507449</v>
       </c>
       <c r="J6" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="K6" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02452699057983965</v>
+        <v>0.02453891521797602</v>
       </c>
       <c r="M6" t="n">
-        <v>2.216202005640651</v>
+        <v>2.210669764443072</v>
       </c>
       <c r="N6" t="n">
-        <v>8.27125120745926</v>
+        <v>8.247297274113258</v>
       </c>
       <c r="O6" t="n">
-        <v>2.875978304413867</v>
+        <v>2.871810800542622</v>
       </c>
       <c r="P6" t="n">
-        <v>364.6765588120804</v>
+        <v>364.6745505794867</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -23964,28 +24031,28 @@
         <v>0.1142</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.003074462267871294</v>
+        <v>-0.003441719890354062</v>
       </c>
       <c r="J7" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="K7" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="L7" t="n">
-        <v>5.329228947192899e-05</v>
+        <v>6.723539335617978e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>2.474169507809212</v>
+        <v>2.468595525158503</v>
       </c>
       <c r="N7" t="n">
-        <v>9.55514152452111</v>
+        <v>9.52818177412203</v>
       </c>
       <c r="O7" t="n">
-        <v>3.09113919526784</v>
+        <v>3.086775303471574</v>
       </c>
       <c r="P7" t="n">
-        <v>362.8453118767236</v>
+        <v>362.8490767828453</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -24046,28 +24113,28 @@
         <v>0.1166</v>
       </c>
       <c r="I8" t="n">
-        <v>0.04126302105024103</v>
+        <v>0.03678112999592602</v>
       </c>
       <c r="J8" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="K8" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="L8" t="n">
-        <v>0.008832620783456258</v>
+        <v>0.006972214724358938</v>
       </c>
       <c r="M8" t="n">
-        <v>2.519229289920161</v>
+        <v>2.533055328136639</v>
       </c>
       <c r="N8" t="n">
-        <v>10.29356403783238</v>
+        <v>10.42142058075069</v>
       </c>
       <c r="O8" t="n">
-        <v>3.208358464671985</v>
+        <v>3.228222511034623</v>
       </c>
       <c r="P8" t="n">
-        <v>361.9109778760358</v>
+        <v>361.9569235502281</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -24128,28 +24195,28 @@
         <v>0.1574</v>
       </c>
       <c r="I9" t="n">
-        <v>0.08727180748053479</v>
+        <v>0.08426744268500655</v>
       </c>
       <c r="J9" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="K9" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04837623827204152</v>
+        <v>0.04516745290350888</v>
       </c>
       <c r="M9" t="n">
-        <v>2.343671085774012</v>
+        <v>2.350882715571814</v>
       </c>
       <c r="N9" t="n">
-        <v>8.071745065587164</v>
+        <v>8.119090529101973</v>
       </c>
       <c r="O9" t="n">
-        <v>2.841081671755876</v>
+        <v>2.849401784428088</v>
       </c>
       <c r="P9" t="n">
-        <v>359.5680427418582</v>
+        <v>359.598841698008</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -24210,28 +24277,28 @@
         <v>0.1396</v>
       </c>
       <c r="I10" t="n">
-        <v>0.08946225241758915</v>
+        <v>0.08435804439464055</v>
       </c>
       <c r="J10" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="K10" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="L10" t="n">
-        <v>0.04148037514789216</v>
+        <v>0.03657129363655309</v>
       </c>
       <c r="M10" t="n">
-        <v>2.180545893898741</v>
+        <v>2.199547770286059</v>
       </c>
       <c r="N10" t="n">
-        <v>9.96378396876068</v>
+        <v>10.13954360988645</v>
       </c>
       <c r="O10" t="n">
-        <v>3.156546208874611</v>
+        <v>3.184265003087283</v>
       </c>
       <c r="P10" t="n">
-        <v>357.7384711341943</v>
+        <v>357.7907964308135</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -24292,28 +24359,28 @@
         <v>0.1321</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.01222734285171158</v>
+        <v>-0.01316355045536685</v>
       </c>
       <c r="J11" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="K11" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0005660430780165537</v>
+        <v>0.0006601682358561289</v>
       </c>
       <c r="M11" t="n">
-        <v>2.87554925095438</v>
+        <v>2.873208473161912</v>
       </c>
       <c r="N11" t="n">
-        <v>14.22181776370277</v>
+        <v>14.18700754698842</v>
       </c>
       <c r="O11" t="n">
-        <v>3.771182541816661</v>
+        <v>3.766564422253842</v>
       </c>
       <c r="P11" t="n">
-        <v>358.4283699143059</v>
+        <v>358.4379673563259</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -24374,28 +24441,28 @@
         <v>0.08840000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>0.03320742472319361</v>
+        <v>0.0310562661159659</v>
       </c>
       <c r="J12" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="K12" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="L12" t="n">
-        <v>0.004018099316027923</v>
+        <v>0.003531511407144583</v>
       </c>
       <c r="M12" t="n">
-        <v>2.957483891225158</v>
+        <v>2.958710916684286</v>
       </c>
       <c r="N12" t="n">
-        <v>14.72609118727725</v>
+        <v>14.71931421716015</v>
       </c>
       <c r="O12" t="n">
-        <v>3.837458949262813</v>
+        <v>3.836575845354833</v>
       </c>
       <c r="P12" t="n">
-        <v>361.9859959661642</v>
+        <v>362.0080483613041</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -24456,28 +24523,28 @@
         <v>0.09229999999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.02817398934807953</v>
+        <v>-0.03057418039996041</v>
       </c>
       <c r="J13" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="K13" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="L13" t="n">
-        <v>0.006209341545781677</v>
+        <v>0.007305994060924692</v>
       </c>
       <c r="M13" t="n">
-        <v>2.035737681759724</v>
+        <v>2.040935158103157</v>
       </c>
       <c r="N13" t="n">
-        <v>6.844352454978315</v>
+        <v>6.869606702055519</v>
       </c>
       <c r="O13" t="n">
-        <v>2.61617133517251</v>
+        <v>2.620993457079876</v>
       </c>
       <c r="P13" t="n">
-        <v>362.0572126935359</v>
+        <v>362.0818180207811</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -24538,28 +24605,28 @@
         <v>0.1044</v>
       </c>
       <c r="I14" t="n">
-        <v>0.01087196036606644</v>
+        <v>0.008157010752333866</v>
       </c>
       <c r="J14" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="K14" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0005699203382639739</v>
+        <v>0.0003214308936607679</v>
       </c>
       <c r="M14" t="n">
-        <v>2.360995727291799</v>
+        <v>2.369040205416511</v>
       </c>
       <c r="N14" t="n">
-        <v>11.16709714282412</v>
+        <v>11.19234212449244</v>
       </c>
       <c r="O14" t="n">
-        <v>3.341720685937728</v>
+        <v>3.345495796513939</v>
       </c>
       <c r="P14" t="n">
-        <v>362.4810450456505</v>
+        <v>362.5088770899571</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -24620,28 +24687,28 @@
         <v>0.1029</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.02059413662288526</v>
+        <v>-0.02096422487574704</v>
       </c>
       <c r="J15" t="n">
+        <v>341</v>
+      </c>
+      <c r="K15" t="n">
         <v>340</v>
       </c>
-      <c r="K15" t="n">
-        <v>339</v>
-      </c>
       <c r="L15" t="n">
-        <v>0.002164704406593332</v>
+        <v>0.002258167914197196</v>
       </c>
       <c r="M15" t="n">
-        <v>2.392184496355136</v>
+        <v>2.38706187698886</v>
       </c>
       <c r="N15" t="n">
-        <v>10.56033318677903</v>
+        <v>10.53035484938897</v>
       </c>
       <c r="O15" t="n">
-        <v>3.249666627021768</v>
+        <v>3.245050823852991</v>
       </c>
       <c r="P15" t="n">
-        <v>365.5886402017324</v>
+        <v>365.5924309363623</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -24702,28 +24769,28 @@
         <v>0.1246</v>
       </c>
       <c r="I16" t="n">
-        <v>0.01134243605570022</v>
+        <v>0.01181727031219595</v>
       </c>
       <c r="J16" t="n">
+        <v>341</v>
+      </c>
+      <c r="K16" t="n">
         <v>340</v>
       </c>
-      <c r="K16" t="n">
-        <v>339</v>
-      </c>
       <c r="L16" t="n">
-        <v>0.000903849614763752</v>
+        <v>0.0009875361419235951</v>
       </c>
       <c r="M16" t="n">
-        <v>2.203201759692978</v>
+        <v>2.198878479634533</v>
       </c>
       <c r="N16" t="n">
-        <v>7.681640325597633</v>
+        <v>7.660827537961366</v>
       </c>
       <c r="O16" t="n">
-        <v>2.771577227067222</v>
+        <v>2.767819997391696</v>
       </c>
       <c r="P16" t="n">
-        <v>361.9480594730353</v>
+        <v>361.9431958475469</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -24765,7 +24832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q341"/>
+  <dimension ref="A1:Q342"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54423,6 +54490,93 @@
         </is>
       </c>
     </row>
+    <row r="342">
+      <c r="A342" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:11:45+00:00</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>-35.221195070940134,174.05921177359656</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>-35.221799777315226,174.05868052667472</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>-35.222503521309896,174.058351073322</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>-35.223257938013305,174.05829753433397</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>-35.22399154734183,174.0582982118897</t>
+        </is>
+      </c>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t>-35.22472549865926,174.05830669767565</t>
+        </is>
+      </c>
+      <c r="H342" t="inlineStr">
+        <is>
+          <t>-35.22546105426291,174.05825679151434</t>
+        </is>
+      </c>
+      <c r="I342" t="inlineStr">
+        <is>
+          <t>-35.22619446664217,174.05829570205577</t>
+        </is>
+      </c>
+      <c r="J342" t="inlineStr">
+        <is>
+          <t>-35.22692993674866,174.05826822200507</t>
+        </is>
+      </c>
+      <c r="K342" t="inlineStr">
+        <is>
+          <t>-35.22766161801575,174.05835174182954</t>
+        </is>
+      </c>
+      <c r="L342" t="inlineStr">
+        <is>
+          <t>-35.228396663116186,174.0584133515507</t>
+        </is>
+      </c>
+      <c r="M342" t="inlineStr">
+        <is>
+          <t>-35.22912668276793,174.0585610501555</t>
+        </is>
+      </c>
+      <c r="N342" t="inlineStr">
+        <is>
+          <t>-35.229828270573904,174.0588384890195</t>
+        </is>
+      </c>
+      <c r="O342" t="inlineStr">
+        <is>
+          <t>-35.23048036943144,174.05924702454428</t>
+        </is>
+      </c>
+      <c r="P342" t="inlineStr">
+        <is>
+          <t>-35.231094955372356,174.05973590046838</t>
+        </is>
+      </c>
+      <c r="Q342" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0063/nzd0063.xlsx
+++ b/data/nzd0063/nzd0063.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q342"/>
+  <dimension ref="A1:Q344"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19946,6 +19946,120 @@
       <c r="Q342" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:12:06+00:00</t>
+        </is>
+      </c>
+      <c r="B343" t="n">
+        <v>359.51</v>
+      </c>
+      <c r="C343" t="n">
+        <v>344.23</v>
+      </c>
+      <c r="D343" t="n">
+        <v>352.18</v>
+      </c>
+      <c r="E343" t="n">
+        <v>359.56</v>
+      </c>
+      <c r="F343" t="n">
+        <v>362.88</v>
+      </c>
+      <c r="G343" t="n">
+        <v>362.49</v>
+      </c>
+      <c r="H343" t="n">
+        <v>355.64</v>
+      </c>
+      <c r="I343" t="n">
+        <v>357.65</v>
+      </c>
+      <c r="J343" t="n">
+        <v>351.93</v>
+      </c>
+      <c r="K343" t="n">
+        <v>355.7</v>
+      </c>
+      <c r="L343" t="n">
+        <v>359.44</v>
+      </c>
+      <c r="M343" t="n">
+        <v>359.45</v>
+      </c>
+      <c r="N343" t="n">
+        <v>359.66</v>
+      </c>
+      <c r="O343" t="n">
+        <v>364.41</v>
+      </c>
+      <c r="P343" t="n">
+        <v>362.99</v>
+      </c>
+      <c r="Q343" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-16 22:11:33+00:00</t>
+        </is>
+      </c>
+      <c r="B344" t="n">
+        <v>359.73</v>
+      </c>
+      <c r="C344" t="n">
+        <v>343.36</v>
+      </c>
+      <c r="D344" t="n">
+        <v>350.79</v>
+      </c>
+      <c r="E344" t="n">
+        <v>358.74</v>
+      </c>
+      <c r="F344" t="n">
+        <v>362.18</v>
+      </c>
+      <c r="G344" t="n">
+        <v>360.59</v>
+      </c>
+      <c r="H344" t="n">
+        <v>360.98</v>
+      </c>
+      <c r="I344" t="n">
+        <v>361.92</v>
+      </c>
+      <c r="J344" t="n">
+        <v>356.8</v>
+      </c>
+      <c r="K344" t="n">
+        <v>354.75</v>
+      </c>
+      <c r="L344" t="n">
+        <v>357.98</v>
+      </c>
+      <c r="M344" t="n">
+        <v>359.01</v>
+      </c>
+      <c r="N344" t="n">
+        <v>359.23</v>
+      </c>
+      <c r="O344" t="n">
+        <v>363.36</v>
+      </c>
+      <c r="P344" t="n">
+        <v>361.44</v>
+      </c>
+      <c r="Q344" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -19960,7 +20074,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B349"/>
+  <dimension ref="A1:B351"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23453,6 +23567,26 @@
       </c>
       <c r="B349" t="n">
         <v>1.14</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B350" t="n">
+        <v>0.66</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>2026-01-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B351" t="n">
+        <v>-0.06</v>
       </c>
     </row>
   </sheetData>
@@ -23621,28 +23755,28 @@
         <v>0.0544</v>
       </c>
       <c r="I2" t="n">
-        <v>0.04914945344893933</v>
+        <v>0.05342126794477797</v>
       </c>
       <c r="J2" t="n">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="K2" t="n">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="L2" t="n">
-        <v>0.009323211074263926</v>
+        <v>0.01108804564851995</v>
       </c>
       <c r="M2" t="n">
-        <v>2.907240817367021</v>
+        <v>2.911395254172703</v>
       </c>
       <c r="N2" t="n">
-        <v>13.88321336145493</v>
+        <v>13.87454761040312</v>
       </c>
       <c r="O2" t="n">
-        <v>3.72601843278518</v>
+        <v>3.724855381139397</v>
       </c>
       <c r="P2" t="n">
-        <v>354.7693528568586</v>
+        <v>354.7253803220663</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -23703,28 +23837,28 @@
         <v>0.06</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.02715801826354193</v>
+        <v>-0.02690012855440676</v>
       </c>
       <c r="J3" t="n">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="K3" t="n">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="L3" t="n">
-        <v>0.004087631417205251</v>
+        <v>0.004065128887318914</v>
       </c>
       <c r="M3" t="n">
-        <v>2.262168622277435</v>
+        <v>2.251467435414641</v>
       </c>
       <c r="N3" t="n">
-        <v>9.719226228827383</v>
+        <v>9.663916226426279</v>
       </c>
       <c r="O3" t="n">
-        <v>3.117567357544562</v>
+        <v>3.10868400234348</v>
       </c>
       <c r="P3" t="n">
-        <v>344.2973503443375</v>
+        <v>344.2946982238709</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -23785,28 +23919,28 @@
         <v>0.06279999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>0.006508551121326791</v>
+        <v>0.005976104436400813</v>
       </c>
       <c r="J4" t="n">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="K4" t="n">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0001696372268977786</v>
+        <v>0.0001449462030785886</v>
       </c>
       <c r="M4" t="n">
-        <v>2.72343760436847</v>
+        <v>2.711760220521038</v>
       </c>
       <c r="N4" t="n">
-        <v>13.5393319390674</v>
+        <v>13.46413893664677</v>
       </c>
       <c r="O4" t="n">
-        <v>3.679583120282433</v>
+        <v>3.669351296434667</v>
       </c>
       <c r="P4" t="n">
-        <v>351.7551973373833</v>
+        <v>351.7606775615178</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -23867,28 +24001,28 @@
         <v>0.09859999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.02341618212342861</v>
+        <v>-0.02179598475971121</v>
       </c>
       <c r="J5" t="n">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="K5" t="n">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="L5" t="n">
-        <v>0.00321338982426167</v>
+        <v>0.002820053119716781</v>
       </c>
       <c r="M5" t="n">
-        <v>2.326231880058694</v>
+        <v>2.32008990957126</v>
       </c>
       <c r="N5" t="n">
-        <v>9.199349043193488</v>
+        <v>9.157081193874831</v>
       </c>
       <c r="O5" t="n">
-        <v>3.033042868670584</v>
+        <v>3.026066951320613</v>
       </c>
       <c r="P5" t="n">
-        <v>358.4176726809002</v>
+        <v>358.4009975182984</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -23949,28 +24083,28 @@
         <v>0.0949</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.06193490271507449</v>
+        <v>-0.06254926412572533</v>
       </c>
       <c r="J6" t="n">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="K6" t="n">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02453891521797602</v>
+        <v>0.02534515127165782</v>
       </c>
       <c r="M6" t="n">
-        <v>2.210669764443072</v>
+        <v>2.200646334381769</v>
       </c>
       <c r="N6" t="n">
-        <v>8.247297274113258</v>
+        <v>8.20140381553956</v>
       </c>
       <c r="O6" t="n">
-        <v>2.871810800542622</v>
+        <v>2.863809318990977</v>
       </c>
       <c r="P6" t="n">
-        <v>364.6745505794867</v>
+        <v>364.6808764788331</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -24031,28 +24165,28 @@
         <v>0.1142</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.003441719890354062</v>
+        <v>-0.004906461971880529</v>
       </c>
       <c r="J7" t="n">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="K7" t="n">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="L7" t="n">
-        <v>6.723539335617978e-05</v>
+        <v>0.0001383140277296802</v>
       </c>
       <c r="M7" t="n">
-        <v>2.468595525158503</v>
+        <v>2.460804731731105</v>
       </c>
       <c r="N7" t="n">
-        <v>9.52818177412203</v>
+        <v>9.486333735784861</v>
       </c>
       <c r="O7" t="n">
-        <v>3.086775303471574</v>
+        <v>3.079989242803432</v>
       </c>
       <c r="P7" t="n">
-        <v>362.8490767828453</v>
+        <v>362.8641594778762</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -24113,28 +24247,28 @@
         <v>0.1166</v>
       </c>
       <c r="I8" t="n">
-        <v>0.03678112999592602</v>
+        <v>0.03123905230875532</v>
       </c>
       <c r="J8" t="n">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="K8" t="n">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="L8" t="n">
-        <v>0.006972214724358938</v>
+        <v>0.005029398689592068</v>
       </c>
       <c r="M8" t="n">
-        <v>2.533055328136639</v>
+        <v>2.545647894186195</v>
       </c>
       <c r="N8" t="n">
-        <v>10.42142058075069</v>
+        <v>10.52392420458792</v>
       </c>
       <c r="O8" t="n">
-        <v>3.228222511034623</v>
+        <v>3.244059833694182</v>
       </c>
       <c r="P8" t="n">
-        <v>361.9569235502281</v>
+        <v>362.0139557128559</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -24195,28 +24329,28 @@
         <v>0.1574</v>
       </c>
       <c r="I9" t="n">
-        <v>0.08426744268500655</v>
+        <v>0.08182038728337816</v>
       </c>
       <c r="J9" t="n">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="K9" t="n">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04516745290350888</v>
+        <v>0.04299861109613401</v>
       </c>
       <c r="M9" t="n">
-        <v>2.350882715571814</v>
+        <v>2.349336689189502</v>
       </c>
       <c r="N9" t="n">
-        <v>8.119090529101973</v>
+        <v>8.122113023295194</v>
       </c>
       <c r="O9" t="n">
-        <v>2.849401784428088</v>
+        <v>2.849932108541394</v>
       </c>
       <c r="P9" t="n">
-        <v>359.598841698008</v>
+        <v>359.6240183044377</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -24277,28 +24411,28 @@
         <v>0.1396</v>
       </c>
       <c r="I10" t="n">
-        <v>0.08435804439464055</v>
+        <v>0.07756770436236196</v>
       </c>
       <c r="J10" t="n">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="K10" t="n">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="L10" t="n">
-        <v>0.03657129363655309</v>
+        <v>0.03086734165704674</v>
       </c>
       <c r="M10" t="n">
-        <v>2.199547770286059</v>
+        <v>2.220974859720691</v>
       </c>
       <c r="N10" t="n">
-        <v>10.13954360988645</v>
+        <v>10.29754512003872</v>
       </c>
       <c r="O10" t="n">
-        <v>3.184265003087283</v>
+        <v>3.20897882823161</v>
       </c>
       <c r="P10" t="n">
-        <v>357.7907964308135</v>
+        <v>357.8606789254867</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -24359,28 +24493,28 @@
         <v>0.1321</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.01316355045536685</v>
+        <v>-0.01661001477909517</v>
       </c>
       <c r="J11" t="n">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="K11" t="n">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0006601682358561289</v>
+        <v>0.001061526509715915</v>
       </c>
       <c r="M11" t="n">
-        <v>2.873208473161912</v>
+        <v>2.878720942980644</v>
       </c>
       <c r="N11" t="n">
-        <v>14.18700754698842</v>
+        <v>14.15258460856489</v>
       </c>
       <c r="O11" t="n">
-        <v>3.766564422253842</v>
+        <v>3.76199210639322</v>
       </c>
       <c r="P11" t="n">
-        <v>358.4379673563259</v>
+        <v>358.4734462048158</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -24441,28 +24575,28 @@
         <v>0.08840000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>0.0310562661159659</v>
+        <v>0.02610951645113393</v>
       </c>
       <c r="J12" t="n">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="K12" t="n">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="L12" t="n">
-        <v>0.003531511407144583</v>
+        <v>0.00251586973242679</v>
       </c>
       <c r="M12" t="n">
-        <v>2.958710916684286</v>
+        <v>2.963918502847737</v>
       </c>
       <c r="N12" t="n">
-        <v>14.71931421716015</v>
+        <v>14.7334118340431</v>
       </c>
       <c r="O12" t="n">
-        <v>3.836575845354833</v>
+        <v>3.838412671149768</v>
       </c>
       <c r="P12" t="n">
-        <v>362.0080483613041</v>
+        <v>362.0589718502904</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -24523,28 +24657,28 @@
         <v>0.09229999999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.03057418039996041</v>
+        <v>-0.03303048857782972</v>
       </c>
       <c r="J13" t="n">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="K13" t="n">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="L13" t="n">
-        <v>0.007305994060924692</v>
+        <v>0.008602800783944597</v>
       </c>
       <c r="M13" t="n">
-        <v>2.040935158103157</v>
+        <v>2.040533313379434</v>
       </c>
       <c r="N13" t="n">
-        <v>6.869606702055519</v>
+        <v>6.853708726382687</v>
       </c>
       <c r="O13" t="n">
-        <v>2.620993457079876</v>
+        <v>2.617958885540926</v>
       </c>
       <c r="P13" t="n">
-        <v>362.0818180207811</v>
+        <v>362.1071032710239</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -24605,28 +24739,28 @@
         <v>0.1044</v>
       </c>
       <c r="I14" t="n">
-        <v>0.008157010752333866</v>
+        <v>0.004211932074304182</v>
       </c>
       <c r="J14" t="n">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="K14" t="n">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0003214308936607679</v>
+        <v>8.642198661334977e-05</v>
       </c>
       <c r="M14" t="n">
-        <v>2.369040205416511</v>
+        <v>2.377260805653971</v>
       </c>
       <c r="N14" t="n">
-        <v>11.19234212449244</v>
+        <v>11.18893534614244</v>
       </c>
       <c r="O14" t="n">
-        <v>3.345495796513939</v>
+        <v>3.344986598798632</v>
       </c>
       <c r="P14" t="n">
-        <v>362.5088770899571</v>
+        <v>362.549486955115</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -24687,28 +24821,28 @@
         <v>0.1029</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.02096422487574704</v>
+        <v>-0.02235179848449219</v>
       </c>
       <c r="J15" t="n">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="K15" t="n">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="L15" t="n">
-        <v>0.002258167914197196</v>
+        <v>0.002599123216277976</v>
       </c>
       <c r="M15" t="n">
-        <v>2.38706187698886</v>
+        <v>2.380229727438224</v>
       </c>
       <c r="N15" t="n">
-        <v>10.53035484938897</v>
+        <v>10.47803509225018</v>
       </c>
       <c r="O15" t="n">
-        <v>3.245050823852991</v>
+        <v>3.236979316005924</v>
       </c>
       <c r="P15" t="n">
-        <v>365.5924309363623</v>
+        <v>365.6067051875308</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -24769,28 +24903,28 @@
         <v>0.1246</v>
       </c>
       <c r="I16" t="n">
-        <v>0.01181727031219595</v>
+        <v>0.01176694660127217</v>
       </c>
       <c r="J16" t="n">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="K16" t="n">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0009875361419235951</v>
+        <v>0.0009921574264813993</v>
       </c>
       <c r="M16" t="n">
-        <v>2.198878479634533</v>
+        <v>2.190550510095754</v>
       </c>
       <c r="N16" t="n">
-        <v>7.660827537961366</v>
+        <v>7.619525031537405</v>
       </c>
       <c r="O16" t="n">
-        <v>2.767819997391696</v>
+        <v>2.760348715567909</v>
       </c>
       <c r="P16" t="n">
-        <v>361.9431958475469</v>
+        <v>361.9437178330139</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -24832,7 +24966,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q342"/>
+  <dimension ref="A1:Q344"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54577,6 +54711,180 @@
         </is>
       </c>
     </row>
+    <row r="343">
+      <c r="A343" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:12:06+00:00</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>-35.22120919198435,174.05924653157146</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>-35.221803977468966,174.05869098807835</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>-35.22250694316423,174.05836461960808</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>-35.223258211245714,174.05830103449298</t>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>-35.223991523219645,174.05829282810572</t>
+        </is>
+      </c>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>-35.2247254057174,174.05831032180652</t>
+        </is>
+      </c>
+      <c r="H343" t="inlineStr">
+        <is>
+          <t>-35.22546104835759,174.05825701114998</t>
+        </is>
+      </c>
+      <c r="I343" t="inlineStr">
+        <is>
+          <t>-35.22619422175274,174.05830371757742</t>
+        </is>
+      </c>
+      <c r="J343" t="inlineStr">
+        <is>
+          <t>-35.226929849862586,174.05827085696814</t>
+        </is>
+      </c>
+      <c r="K343" t="inlineStr">
+        <is>
+          <t>-35.227661939259534,174.05834219031348</t>
+        </is>
+      </c>
+      <c r="L343" t="inlineStr">
+        <is>
+          <t>-35.22839653573382,174.05841466094853</t>
+        </is>
+      </c>
+      <c r="M343" t="inlineStr">
+        <is>
+          <t>-35.2291220278648,174.05858319028076</t>
+        </is>
+      </c>
+      <c r="N343" t="inlineStr">
+        <is>
+          <t>-35.229824001011764,174.05885249787048</t>
+        </is>
+      </c>
+      <c r="O343" t="inlineStr">
+        <is>
+          <t>-35.23048049955252,174.05924673554574</t>
+        </is>
+      </c>
+      <c r="P343" t="inlineStr">
+        <is>
+          <t>-35.23109515881239,174.05973553754092</t>
+        </is>
+      </c>
+      <c r="Q343" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-16 22:11:33+00:00</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>-35.22121007204909,174.05924869779125</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>-35.22180053017304,174.0586824018319</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>-35.222503256049805,174.05835002322235</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>-35.223257511087475,174.05829206533554</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>-35.22399148875896,174.05828513698577</t>
+        </is>
+      </c>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>-35.22472594083571,174.05828945559827</t>
+        </is>
+      </c>
+      <c r="H344" t="inlineStr">
+        <is>
+          <t>-35.22545947161986,174.05831565386728</t>
+        </is>
+      </c>
+      <c r="I344" t="inlineStr">
+        <is>
+          <t>-35.22619278930676,174.05835060288783</t>
+        </is>
+      </c>
+      <c r="J344" t="inlineStr">
+        <is>
+          <t>-35.22692808678693,174.0583243247592</t>
+        </is>
+      </c>
+      <c r="K344" t="inlineStr">
+        <is>
+          <t>-35.22766229004212,174.05833176049694</t>
+        </is>
+      </c>
+      <c r="L344" t="inlineStr">
+        <is>
+          <t>-35.228398085551746,174.05839872994164</t>
+        </is>
+      </c>
+      <c r="M344" t="inlineStr">
+        <is>
+          <t>-35.22912301255618,174.05857850679294</t>
+        </is>
+      </c>
+      <c r="N344" t="inlineStr">
+        <is>
+          <t>-35.22982535094703,174.05884806860158</t>
+        </is>
+      </c>
+      <c r="O344" t="inlineStr">
+        <is>
+          <t>-35.23048505378986,174.05923662059678</t>
+        </is>
+      </c>
+      <c r="P344" t="inlineStr">
+        <is>
+          <t>-35.23110304211304,174.05972147409963</t>
+        </is>
+      </c>
+      <c r="Q344" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0063/nzd0063.xlsx
+++ b/data/nzd0063/nzd0063.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q344"/>
+  <dimension ref="A1:Q346"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20060,6 +20060,120 @@
       <c r="Q344" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:11:34+00:00</t>
+        </is>
+      </c>
+      <c r="B345" t="n">
+        <v>366.42</v>
+      </c>
+      <c r="C345" t="n">
+        <v>344.84</v>
+      </c>
+      <c r="D345" t="n">
+        <v>355</v>
+      </c>
+      <c r="E345" t="n">
+        <v>359.95</v>
+      </c>
+      <c r="F345" t="n">
+        <v>363.94</v>
+      </c>
+      <c r="G345" t="n">
+        <v>361.11</v>
+      </c>
+      <c r="H345" t="n">
+        <v>364.31</v>
+      </c>
+      <c r="I345" t="n">
+        <v>362.31</v>
+      </c>
+      <c r="J345" t="n">
+        <v>359.77</v>
+      </c>
+      <c r="K345" t="n">
+        <v>357.41</v>
+      </c>
+      <c r="L345" t="n">
+        <v>359.96</v>
+      </c>
+      <c r="M345" t="n">
+        <v>362.16</v>
+      </c>
+      <c r="N345" t="n">
+        <v>359.34</v>
+      </c>
+      <c r="O345" t="n">
+        <v>363.8</v>
+      </c>
+      <c r="P345" t="n">
+        <v>361.45</v>
+      </c>
+      <c r="Q345" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:11:43+00:00</t>
+        </is>
+      </c>
+      <c r="B346" t="n">
+        <v>366.42</v>
+      </c>
+      <c r="C346" t="n">
+        <v>344.84</v>
+      </c>
+      <c r="D346" t="n">
+        <v>355</v>
+      </c>
+      <c r="E346" t="n">
+        <v>359.95</v>
+      </c>
+      <c r="F346" t="n">
+        <v>363.99</v>
+      </c>
+      <c r="G346" t="n">
+        <v>361.56</v>
+      </c>
+      <c r="H346" t="n">
+        <v>363.7</v>
+      </c>
+      <c r="I346" t="n">
+        <v>362.15</v>
+      </c>
+      <c r="J346" t="n">
+        <v>359.15</v>
+      </c>
+      <c r="K346" t="n">
+        <v>356.64</v>
+      </c>
+      <c r="L346" t="n">
+        <v>360.79</v>
+      </c>
+      <c r="M346" t="n">
+        <v>360.54</v>
+      </c>
+      <c r="N346" t="n">
+        <v>359.13</v>
+      </c>
+      <c r="O346" t="n">
+        <v>363.01</v>
+      </c>
+      <c r="P346" t="n">
+        <v>360.97</v>
+      </c>
+      <c r="Q346" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -20074,7 +20188,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B351"/>
+  <dimension ref="A1:B353"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23587,6 +23701,26 @@
       </c>
       <c r="B351" t="n">
         <v>-0.06</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B352" t="n">
+        <v>1.01</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B353" t="n">
+        <v>-0.54</v>
       </c>
     </row>
   </sheetData>
@@ -23755,28 +23889,28 @@
         <v>0.0544</v>
       </c>
       <c r="I2" t="n">
-        <v>0.05342126794477797</v>
+        <v>0.06574687487879625</v>
       </c>
       <c r="J2" t="n">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="K2" t="n">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01108804564851995</v>
+        <v>0.01623331668556005</v>
       </c>
       <c r="M2" t="n">
-        <v>2.911395254172703</v>
+        <v>2.956332866914202</v>
       </c>
       <c r="N2" t="n">
-        <v>13.87454761040312</v>
+        <v>14.39445740742225</v>
       </c>
       <c r="O2" t="n">
-        <v>3.724855381139397</v>
+        <v>3.794002821219596</v>
       </c>
       <c r="P2" t="n">
-        <v>354.7253803220663</v>
+        <v>354.5974760718431</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -23837,28 +23971,28 @@
         <v>0.06</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.02690012855440676</v>
+        <v>-0.02539338121872315</v>
       </c>
       <c r="J3" t="n">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="K3" t="n">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="L3" t="n">
-        <v>0.004065128887318914</v>
+        <v>0.003670883396927005</v>
       </c>
       <c r="M3" t="n">
-        <v>2.251467435414641</v>
+        <v>2.245462392219698</v>
       </c>
       <c r="N3" t="n">
-        <v>9.663916226426279</v>
+        <v>9.616864975067715</v>
       </c>
       <c r="O3" t="n">
-        <v>3.10868400234348</v>
+        <v>3.101107056369985</v>
       </c>
       <c r="P3" t="n">
-        <v>344.2946982238709</v>
+        <v>344.2790625302716</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -23919,28 +24053,28 @@
         <v>0.06279999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>0.005976104436400813</v>
+        <v>0.009667207824536483</v>
       </c>
       <c r="J4" t="n">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="K4" t="n">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0001449462030785886</v>
+        <v>0.0003829230505781878</v>
       </c>
       <c r="M4" t="n">
-        <v>2.711760220521038</v>
+        <v>2.712491538479719</v>
       </c>
       <c r="N4" t="n">
-        <v>13.46413893664677</v>
+        <v>13.43988733800935</v>
       </c>
       <c r="O4" t="n">
-        <v>3.669351296434667</v>
+        <v>3.666045190393777</v>
       </c>
       <c r="P4" t="n">
-        <v>351.7606775615178</v>
+        <v>351.7224045621568</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -24001,28 +24135,28 @@
         <v>0.09859999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.02179598475971121</v>
+        <v>-0.01924094305375718</v>
       </c>
       <c r="J5" t="n">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="K5" t="n">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="L5" t="n">
-        <v>0.002820053119716781</v>
+        <v>0.00222323478314701</v>
       </c>
       <c r="M5" t="n">
-        <v>2.32008990957126</v>
+        <v>2.318138308406448</v>
       </c>
       <c r="N5" t="n">
-        <v>9.157081193874831</v>
+        <v>9.129794182772924</v>
       </c>
       <c r="O5" t="n">
-        <v>3.026066951320613</v>
+        <v>3.021554927975483</v>
       </c>
       <c r="P5" t="n">
-        <v>358.4009975182984</v>
+        <v>358.3744835526806</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -24083,28 +24217,28 @@
         <v>0.0949</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.06254926412572533</v>
+        <v>-0.06141588280813072</v>
       </c>
       <c r="J6" t="n">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="K6" t="n">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02534515127165782</v>
+        <v>0.02477383795321342</v>
       </c>
       <c r="M6" t="n">
-        <v>2.200646334381769</v>
+        <v>2.193475889483961</v>
       </c>
       <c r="N6" t="n">
-        <v>8.20140381553956</v>
+        <v>8.158938683961768</v>
       </c>
       <c r="O6" t="n">
-        <v>2.863809318990977</v>
+        <v>2.856385597912468</v>
       </c>
       <c r="P6" t="n">
-        <v>364.6808764788331</v>
+        <v>364.6691151152477</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -24165,28 +24299,28 @@
         <v>0.1142</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.004906461971880529</v>
+        <v>-0.006580622418977829</v>
       </c>
       <c r="J7" t="n">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="K7" t="n">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0001383140277296802</v>
+        <v>0.0002519346183268434</v>
       </c>
       <c r="M7" t="n">
-        <v>2.460804731731105</v>
+        <v>2.454061716082281</v>
       </c>
       <c r="N7" t="n">
-        <v>9.486333735784861</v>
+        <v>9.442715183466902</v>
       </c>
       <c r="O7" t="n">
-        <v>3.079989242803432</v>
+        <v>3.072900125852922</v>
       </c>
       <c r="P7" t="n">
-        <v>362.8641594778762</v>
+        <v>362.8815311745976</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -24247,28 +24381,28 @@
         <v>0.1166</v>
       </c>
       <c r="I8" t="n">
-        <v>0.03123905230875532</v>
+        <v>0.03263305494157087</v>
       </c>
       <c r="J8" t="n">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="K8" t="n">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="L8" t="n">
-        <v>0.005029398689592068</v>
+        <v>0.005557269954222455</v>
       </c>
       <c r="M8" t="n">
-        <v>2.545647894186195</v>
+        <v>2.537340637676643</v>
       </c>
       <c r="N8" t="n">
-        <v>10.52392420458792</v>
+        <v>10.47114004802864</v>
       </c>
       <c r="O8" t="n">
-        <v>3.244059833694182</v>
+        <v>3.235914097751769</v>
       </c>
       <c r="P8" t="n">
-        <v>362.0139557128559</v>
+        <v>361.9994916918563</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -24329,28 +24463,28 @@
         <v>0.1574</v>
       </c>
       <c r="I9" t="n">
-        <v>0.08182038728337816</v>
+        <v>0.08233315262064918</v>
       </c>
       <c r="J9" t="n">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="K9" t="n">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04299861109613401</v>
+        <v>0.04408850970899403</v>
       </c>
       <c r="M9" t="n">
-        <v>2.349336689189502</v>
+        <v>2.338208381451286</v>
       </c>
       <c r="N9" t="n">
-        <v>8.122113023295194</v>
+        <v>8.076105326899594</v>
       </c>
       <c r="O9" t="n">
-        <v>2.849932108541394</v>
+        <v>2.841848927529328</v>
       </c>
       <c r="P9" t="n">
-        <v>359.6240183044377</v>
+        <v>359.6186977289246</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -24411,28 +24545,28 @@
         <v>0.1396</v>
       </c>
       <c r="I10" t="n">
-        <v>0.07756770436236196</v>
+        <v>0.07701620696538097</v>
       </c>
       <c r="J10" t="n">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="K10" t="n">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="L10" t="n">
-        <v>0.03086734165704674</v>
+        <v>0.03084839760715297</v>
       </c>
       <c r="M10" t="n">
-        <v>2.220974859720691</v>
+        <v>2.210859358482879</v>
       </c>
       <c r="N10" t="n">
-        <v>10.29754512003872</v>
+        <v>10.23961388683967</v>
       </c>
       <c r="O10" t="n">
-        <v>3.20897882823161</v>
+        <v>3.19993966924998</v>
       </c>
       <c r="P10" t="n">
-        <v>357.8606789254867</v>
+        <v>357.8664036204034</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -24493,28 +24627,28 @@
         <v>0.1321</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.01661001477909517</v>
+        <v>-0.01781398695826572</v>
       </c>
       <c r="J11" t="n">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="K11" t="n">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="L11" t="n">
-        <v>0.001061526509715915</v>
+        <v>0.001237175043843575</v>
       </c>
       <c r="M11" t="n">
-        <v>2.878720942980644</v>
+        <v>2.869676843630305</v>
       </c>
       <c r="N11" t="n">
-        <v>14.15258460856489</v>
+        <v>14.07711630913541</v>
       </c>
       <c r="O11" t="n">
-        <v>3.76199210639322</v>
+        <v>3.751948335083442</v>
       </c>
       <c r="P11" t="n">
-        <v>358.4734462048158</v>
+        <v>358.4859421044443</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -24575,28 +24709,28 @@
         <v>0.08840000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>0.02610951645113393</v>
+        <v>0.02325896778511076</v>
       </c>
       <c r="J12" t="n">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="K12" t="n">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="L12" t="n">
-        <v>0.00251586973242679</v>
+        <v>0.002020707056372473</v>
       </c>
       <c r="M12" t="n">
-        <v>2.963918502847737</v>
+        <v>2.959571136913625</v>
       </c>
       <c r="N12" t="n">
-        <v>14.7334118340431</v>
+        <v>14.68112265899221</v>
       </c>
       <c r="O12" t="n">
-        <v>3.838412671149768</v>
+        <v>3.831595315138618</v>
       </c>
       <c r="P12" t="n">
-        <v>362.0589718502904</v>
+        <v>362.088550004001</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -24657,28 +24791,28 @@
         <v>0.09229999999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.03303048857782972</v>
+        <v>-0.03288212368711768</v>
       </c>
       <c r="J13" t="n">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="K13" t="n">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="L13" t="n">
-        <v>0.008602800783944597</v>
+        <v>0.00863899368838239</v>
       </c>
       <c r="M13" t="n">
-        <v>2.040533313379434</v>
+        <v>2.033415465444385</v>
       </c>
       <c r="N13" t="n">
-        <v>6.853708726382687</v>
+        <v>6.817868394248237</v>
       </c>
       <c r="O13" t="n">
-        <v>2.617958885540926</v>
+        <v>2.611104822531688</v>
       </c>
       <c r="P13" t="n">
-        <v>362.1071032710239</v>
+        <v>362.1055681945575</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -24739,28 +24873,28 @@
         <v>0.1044</v>
       </c>
       <c r="I14" t="n">
-        <v>0.004211932074304182</v>
+        <v>0.0001046415844791535</v>
       </c>
       <c r="J14" t="n">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="K14" t="n">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="L14" t="n">
-        <v>8.642198661334977e-05</v>
+        <v>5.376600042961144e-08</v>
       </c>
       <c r="M14" t="n">
-        <v>2.377260805653971</v>
+        <v>2.386539028135054</v>
       </c>
       <c r="N14" t="n">
-        <v>11.18893534614244</v>
+        <v>11.19079853920969</v>
       </c>
       <c r="O14" t="n">
-        <v>3.344986598798632</v>
+        <v>3.345265092516539</v>
       </c>
       <c r="P14" t="n">
-        <v>362.549486955115</v>
+        <v>362.5921093829525</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -24821,28 +24955,28 @@
         <v>0.1029</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.02235179848449219</v>
+        <v>-0.02428118235198683</v>
       </c>
       <c r="J15" t="n">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="K15" t="n">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="L15" t="n">
-        <v>0.002599123216277976</v>
+        <v>0.003103570863113858</v>
       </c>
       <c r="M15" t="n">
-        <v>2.380229727438224</v>
+        <v>2.376095041457006</v>
       </c>
       <c r="N15" t="n">
-        <v>10.47803509225018</v>
+        <v>10.43276432242923</v>
       </c>
       <c r="O15" t="n">
-        <v>3.236979316005924</v>
+        <v>3.229978997211782</v>
       </c>
       <c r="P15" t="n">
-        <v>365.6067051875308</v>
+        <v>365.6267131384872</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -24903,28 +25037,28 @@
         <v>0.1246</v>
       </c>
       <c r="I16" t="n">
-        <v>0.01176694660127217</v>
+        <v>0.01051514635025675</v>
       </c>
       <c r="J16" t="n">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="K16" t="n">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0009921574264813993</v>
+        <v>0.0008027542567905499</v>
       </c>
       <c r="M16" t="n">
-        <v>2.190550510095754</v>
+        <v>2.184127117880778</v>
       </c>
       <c r="N16" t="n">
-        <v>7.619525031537405</v>
+        <v>7.581770173845352</v>
       </c>
       <c r="O16" t="n">
-        <v>2.760348715567909</v>
+        <v>2.753501438867493</v>
       </c>
       <c r="P16" t="n">
-        <v>361.9437178330139</v>
+        <v>361.9566990744377</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -24966,7 +25100,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q344"/>
+  <dimension ref="A1:Q346"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54885,6 +55019,180 @@
         </is>
       </c>
     </row>
+    <row r="345">
+      <c r="A345" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:11:34+00:00</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>-35.221236833998816,174.0593145705878</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>-35.221806394538156,174.05869700832054</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>-35.222514423491575,174.0583942324234</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>-35.22325854424755,174.05830530031182</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>-35.223991575402046,174.0583044746588</t>
+        </is>
+      </c>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>-35.22472579438264,174.05829516635</t>
+        </is>
+      </c>
+      <c r="H345" t="inlineStr">
+        <is>
+          <t>-35.225458488358925,174.05835222320073</t>
+        </is>
+      </c>
+      <c r="I345" t="inlineStr">
+        <is>
+          <t>-35.22619265847355,174.0583548851526</t>
+        </is>
+      </c>
+      <c r="J345" t="inlineStr">
+        <is>
+          <t>-35.2269270115526,174.05835693242503</t>
+        </is>
+      </c>
+      <c r="K345" t="inlineStr">
+        <is>
+          <t>-35.22766130784862,174.05836096398295</t>
+        </is>
+      </c>
+      <c r="L345" t="inlineStr">
+        <is>
+          <t>-35.22839598374337,174.05842033500562</t>
+        </is>
+      </c>
+      <c r="M345" t="inlineStr">
+        <is>
+          <t>-35.22911596305711,174.05861203630542</t>
+        </is>
+      </c>
+      <c r="N345" t="inlineStr">
+        <is>
+          <t>-35.22982500561477,174.0588492016704</t>
+        </is>
+      </c>
+      <c r="O345" t="inlineStr">
+        <is>
+          <t>-35.23048314534765,174.0592408592422</t>
+        </is>
+      </c>
+      <c r="P345" t="inlineStr">
+        <is>
+          <t>-35.23110299125303,174.05972156483153</t>
+        </is>
+      </c>
+      <c r="Q345" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:11:43+00:00</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>-35.221236833998816,174.0593145705878</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>-35.221806394538156,174.05869700832054</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>-35.222514423491575,174.0583942324234</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>-35.22325854424755,174.05830530031182</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>-35.223991577863444,174.05830502402452</t>
+        </is>
+      </c>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>-35.224725667644186,174.0583001083467</t>
+        </is>
+      </c>
+      <c r="H346" t="inlineStr">
+        <is>
+          <t>-35.22545866847661,174.0583455243139</t>
+        </is>
+      </c>
+      <c r="I346" t="inlineStr">
+        <is>
+          <t>-35.22619271214873,174.05835312832602</t>
+        </is>
+      </c>
+      <c r="J346" t="inlineStr">
+        <is>
+          <t>-35.22692723601301,174.0583501254376</t>
+        </is>
+      </c>
+      <c r="K346" t="inlineStr">
+        <is>
+          <t>-35.227661592168516,174.05835251034236</t>
+        </is>
+      </c>
+      <c r="L346" t="inlineStr">
+        <is>
+          <t>-35.228395102681134,174.05842939167349</t>
+        </is>
+      </c>
+      <c r="M346" t="inlineStr">
+        <is>
+          <t>-35.22911958851492,174.0585947925569</t>
+        </is>
+      </c>
+      <c r="N346" t="inlineStr">
+        <is>
+          <t>-35.229825664885446,174.05884703853903</t>
+        </is>
+      </c>
+      <c r="O346" t="inlineStr">
+        <is>
+          <t>-35.23048657186879,174.05923324894687</t>
+        </is>
+      </c>
+      <c r="P346" t="inlineStr">
+        <is>
+          <t>-35.23110543253291,174.0597172097008</t>
+        </is>
+      </c>
+      <c r="Q346" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0063/nzd0063.xlsx
+++ b/data/nzd0063/nzd0063.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q346"/>
+  <dimension ref="A1:Q347"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20174,6 +20174,63 @@
       <c r="Q346" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:11:04+00:00</t>
+        </is>
+      </c>
+      <c r="B347" t="n">
+        <v>364.14</v>
+      </c>
+      <c r="C347" t="n">
+        <v>343.63</v>
+      </c>
+      <c r="D347" t="n">
+        <v>353.74</v>
+      </c>
+      <c r="E347" t="n">
+        <v>358.26</v>
+      </c>
+      <c r="F347" t="n">
+        <v>363.05</v>
+      </c>
+      <c r="G347" t="n">
+        <v>359.37</v>
+      </c>
+      <c r="H347" t="n">
+        <v>361.94</v>
+      </c>
+      <c r="I347" t="n">
+        <v>360.95</v>
+      </c>
+      <c r="J347" t="n">
+        <v>357.74</v>
+      </c>
+      <c r="K347" t="n">
+        <v>356.51</v>
+      </c>
+      <c r="L347" t="n">
+        <v>360.08</v>
+      </c>
+      <c r="M347" t="n">
+        <v>359.96</v>
+      </c>
+      <c r="N347" t="n">
+        <v>359.07</v>
+      </c>
+      <c r="O347" t="n">
+        <v>362.84</v>
+      </c>
+      <c r="P347" t="n">
+        <v>360.37</v>
+      </c>
+      <c r="Q347" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -20188,7 +20245,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B353"/>
+  <dimension ref="A1:B354"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23721,6 +23778,16 @@
       </c>
       <c r="B353" t="n">
         <v>-0.54</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B354" t="n">
+        <v>0.13</v>
       </c>
     </row>
   </sheetData>
@@ -23889,28 +23956,28 @@
         <v>0.0544</v>
       </c>
       <c r="I2" t="n">
-        <v>0.06574687487879625</v>
+        <v>0.07042009061035669</v>
       </c>
       <c r="J2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01623331668556005</v>
+        <v>0.01848585888114562</v>
       </c>
       <c r="M2" t="n">
-        <v>2.956332866914202</v>
+        <v>2.971709780700763</v>
       </c>
       <c r="N2" t="n">
-        <v>14.39445740742225</v>
+        <v>14.52640117307892</v>
       </c>
       <c r="O2" t="n">
-        <v>3.794002821219596</v>
+        <v>3.811351620236437</v>
       </c>
       <c r="P2" t="n">
-        <v>354.5974760718431</v>
+        <v>354.5487447296141</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -23971,28 +24038,28 @@
         <v>0.06</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.02539338121872315</v>
+        <v>-0.02537842103680209</v>
       </c>
       <c r="J3" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K3" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003670883396927005</v>
+        <v>0.003691936252166905</v>
       </c>
       <c r="M3" t="n">
-        <v>2.245462392219698</v>
+        <v>2.239041702640344</v>
       </c>
       <c r="N3" t="n">
-        <v>9.616864975067715</v>
+        <v>9.589072346139407</v>
       </c>
       <c r="O3" t="n">
-        <v>3.101107056369985</v>
+        <v>3.096622732290682</v>
       </c>
       <c r="P3" t="n">
-        <v>344.2790625302716</v>
+        <v>344.2789065285402</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -24053,28 +24120,28 @@
         <v>0.06279999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>0.009667207824536483</v>
+        <v>0.01072279320055061</v>
       </c>
       <c r="J4" t="n">
+        <v>346</v>
+      </c>
+      <c r="K4" t="n">
         <v>345</v>
       </c>
-      <c r="K4" t="n">
-        <v>344</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.0003829230505781878</v>
+        <v>0.0004740232905504627</v>
       </c>
       <c r="M4" t="n">
-        <v>2.712491538479719</v>
+        <v>2.70928792055881</v>
       </c>
       <c r="N4" t="n">
-        <v>13.43988733800935</v>
+        <v>13.40981680557029</v>
       </c>
       <c r="O4" t="n">
-        <v>3.666045190393777</v>
+        <v>3.661941671513937</v>
       </c>
       <c r="P4" t="n">
-        <v>351.7224045621568</v>
+        <v>351.7114055078993</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -24135,28 +24202,28 @@
         <v>0.09859999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.01924094305375718</v>
+        <v>-0.01900255047915316</v>
       </c>
       <c r="J5" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K5" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="L5" t="n">
-        <v>0.00222323478314701</v>
+        <v>0.002183518530425754</v>
       </c>
       <c r="M5" t="n">
-        <v>2.318138308406448</v>
+        <v>2.312511923157187</v>
       </c>
       <c r="N5" t="n">
-        <v>9.129794182772924</v>
+        <v>9.103859110057106</v>
       </c>
       <c r="O5" t="n">
-        <v>3.021554927975483</v>
+        <v>3.017260199263084</v>
       </c>
       <c r="P5" t="n">
-        <v>358.3744835526806</v>
+        <v>358.3719976434469</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -24217,28 +24284,28 @@
         <v>0.0949</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.06141588280813072</v>
+        <v>-0.06140148417112069</v>
       </c>
       <c r="J6" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K6" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02477383795321342</v>
+        <v>0.024930136985576</v>
       </c>
       <c r="M6" t="n">
-        <v>2.193475889483961</v>
+        <v>2.187206578015473</v>
       </c>
       <c r="N6" t="n">
-        <v>8.158938683961768</v>
+        <v>8.135359583823673</v>
       </c>
       <c r="O6" t="n">
-        <v>2.856385597912468</v>
+        <v>2.852255175089296</v>
       </c>
       <c r="P6" t="n">
-        <v>364.6691151152477</v>
+        <v>364.6689649691924</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -24299,28 +24366,28 @@
         <v>0.1142</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.006580622418977829</v>
+        <v>-0.008580526888683795</v>
       </c>
       <c r="J7" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K7" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0002519346183268434</v>
+        <v>0.0004297795127290449</v>
       </c>
       <c r="M7" t="n">
-        <v>2.454061716082281</v>
+        <v>2.455836924871428</v>
       </c>
       <c r="N7" t="n">
-        <v>9.442715183466902</v>
+        <v>9.447207624014476</v>
       </c>
       <c r="O7" t="n">
-        <v>3.072900125852922</v>
+        <v>3.073631016243569</v>
       </c>
       <c r="P7" t="n">
-        <v>362.8815311745976</v>
+        <v>362.9023857712473</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -24381,28 +24448,28 @@
         <v>0.1166</v>
       </c>
       <c r="I8" t="n">
-        <v>0.03263305494157087</v>
+        <v>0.03207247411987005</v>
       </c>
       <c r="J8" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K8" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="L8" t="n">
-        <v>0.005557269954222455</v>
+        <v>0.005404784882720448</v>
       </c>
       <c r="M8" t="n">
-        <v>2.537340637676643</v>
+        <v>2.532795795658154</v>
       </c>
       <c r="N8" t="n">
-        <v>10.47114004802864</v>
+        <v>10.44337387603068</v>
       </c>
       <c r="O8" t="n">
-        <v>3.235914097751769</v>
+        <v>3.231620936315192</v>
       </c>
       <c r="P8" t="n">
-        <v>361.9994916918563</v>
+        <v>362.0053373145363</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -24463,28 +24530,28 @@
         <v>0.1574</v>
       </c>
       <c r="I9" t="n">
-        <v>0.08233315262064918</v>
+        <v>0.08181587567846668</v>
       </c>
       <c r="J9" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K9" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04408850970899403</v>
+        <v>0.04383840827226215</v>
       </c>
       <c r="M9" t="n">
-        <v>2.338208381451286</v>
+        <v>2.333905886764712</v>
       </c>
       <c r="N9" t="n">
-        <v>8.076105326899594</v>
+        <v>8.054890307771906</v>
       </c>
       <c r="O9" t="n">
-        <v>2.841848927529328</v>
+        <v>2.838113864483225</v>
       </c>
       <c r="P9" t="n">
-        <v>359.6186977289246</v>
+        <v>359.6240917875654</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -24545,28 +24612,28 @@
         <v>0.1396</v>
       </c>
       <c r="I10" t="n">
-        <v>0.07701620696538097</v>
+        <v>0.07570632174227759</v>
       </c>
       <c r="J10" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K10" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="L10" t="n">
-        <v>0.03084839760715297</v>
+        <v>0.03000110934418321</v>
       </c>
       <c r="M10" t="n">
-        <v>2.210859358482879</v>
+        <v>2.210995641433462</v>
       </c>
       <c r="N10" t="n">
-        <v>10.23961388683967</v>
+        <v>10.2236544669827</v>
       </c>
       <c r="O10" t="n">
-        <v>3.19993966924998</v>
+        <v>3.197444990454519</v>
       </c>
       <c r="P10" t="n">
-        <v>357.8664036204034</v>
+        <v>357.8800628368305</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -24627,28 +24694,28 @@
         <v>0.1321</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.01781398695826572</v>
+        <v>-0.01871435980518077</v>
       </c>
       <c r="J11" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K11" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="L11" t="n">
-        <v>0.001237175043843575</v>
+        <v>0.001374057065297252</v>
       </c>
       <c r="M11" t="n">
-        <v>2.869676843630305</v>
+        <v>2.867034147897305</v>
       </c>
       <c r="N11" t="n">
-        <v>14.07711630913541</v>
+        <v>14.04287311485638</v>
       </c>
       <c r="O11" t="n">
-        <v>3.751948335083442</v>
+        <v>3.747382168241768</v>
       </c>
       <c r="P11" t="n">
-        <v>358.4859421044443</v>
+        <v>358.4953310091852</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -24709,28 +24776,28 @@
         <v>0.08840000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>0.02325896778511076</v>
+        <v>0.02168091588376258</v>
       </c>
       <c r="J12" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K12" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="L12" t="n">
-        <v>0.002020707056372473</v>
+        <v>0.001766064513840204</v>
       </c>
       <c r="M12" t="n">
-        <v>2.959571136913625</v>
+        <v>2.958020472533059</v>
       </c>
       <c r="N12" t="n">
-        <v>14.68112265899221</v>
+        <v>14.65848077232382</v>
       </c>
       <c r="O12" t="n">
-        <v>3.831595315138618</v>
+        <v>3.828639545886217</v>
       </c>
       <c r="P12" t="n">
-        <v>362.088550004001</v>
+        <v>362.1050056079527</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -24791,28 +24858,28 @@
         <v>0.09229999999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.03288212368711768</v>
+        <v>-0.03364185645718355</v>
       </c>
       <c r="J13" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K13" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="L13" t="n">
-        <v>0.00863899368838239</v>
+        <v>0.009095262274701477</v>
       </c>
       <c r="M13" t="n">
-        <v>2.033415465444385</v>
+        <v>2.031080598725668</v>
       </c>
       <c r="N13" t="n">
-        <v>6.817868394248237</v>
+        <v>6.802750324491295</v>
       </c>
       <c r="O13" t="n">
-        <v>2.611104822531688</v>
+        <v>2.608208259417045</v>
       </c>
       <c r="P13" t="n">
-        <v>362.1055681945575</v>
+        <v>362.1134905332098</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -24873,28 +24940,28 @@
         <v>0.1044</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0001046415844791535</v>
+        <v>-0.002009729023665607</v>
       </c>
       <c r="J14" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K14" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="L14" t="n">
-        <v>5.376600042961144e-08</v>
+        <v>1.990626308767673e-05</v>
       </c>
       <c r="M14" t="n">
-        <v>2.386539028135054</v>
+        <v>2.39162759651615</v>
       </c>
       <c r="N14" t="n">
-        <v>11.19079853920969</v>
+        <v>11.19398114769837</v>
       </c>
       <c r="O14" t="n">
-        <v>3.345265092516539</v>
+        <v>3.345740747233469</v>
       </c>
       <c r="P14" t="n">
-        <v>362.5921093829525</v>
+        <v>362.6141576091896</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -24955,28 +25022,28 @@
         <v>0.1029</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.02428118235198683</v>
+        <v>-0.0255671035484699</v>
       </c>
       <c r="J15" t="n">
+        <v>346</v>
+      </c>
+      <c r="K15" t="n">
         <v>345</v>
       </c>
-      <c r="K15" t="n">
-        <v>344</v>
-      </c>
       <c r="L15" t="n">
-        <v>0.003103570863113858</v>
+        <v>0.00345924866669034</v>
       </c>
       <c r="M15" t="n">
-        <v>2.376095041457006</v>
+        <v>2.375666416086085</v>
       </c>
       <c r="N15" t="n">
-        <v>10.43276432242923</v>
+        <v>10.41571099466739</v>
       </c>
       <c r="O15" t="n">
-        <v>3.229978997211782</v>
+        <v>3.227338066374111</v>
       </c>
       <c r="P15" t="n">
-        <v>365.6267131384872</v>
+        <v>365.6401122602753</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -25037,28 +25104,28 @@
         <v>0.1246</v>
       </c>
       <c r="I16" t="n">
-        <v>0.01051514635025675</v>
+        <v>0.009395789683897293</v>
       </c>
       <c r="J16" t="n">
+        <v>346</v>
+      </c>
+      <c r="K16" t="n">
         <v>345</v>
       </c>
-      <c r="K16" t="n">
-        <v>344</v>
-      </c>
       <c r="L16" t="n">
-        <v>0.0008027542567905499</v>
+        <v>0.0006446374221037443</v>
       </c>
       <c r="M16" t="n">
-        <v>2.184127117880778</v>
+        <v>2.183369303736761</v>
       </c>
       <c r="N16" t="n">
-        <v>7.581770173845352</v>
+        <v>7.56978574428642</v>
       </c>
       <c r="O16" t="n">
-        <v>2.753501438867493</v>
+        <v>2.751324361882186</v>
       </c>
       <c r="P16" t="n">
-        <v>361.9566990744377</v>
+        <v>361.9683626167589</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -25100,7 +25167,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q346"/>
+  <dimension ref="A1:Q347"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55193,6 +55260,93 @@
         </is>
       </c>
     </row>
+    <row r="347">
+      <c r="A347" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:11:04+00:00</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>-35.22122771333845,174.05929212066133</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>-35.22180160002356,174.05868506652902</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>-35.22251108121856,174.05838100116483</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>-35.22325710123846,174.05828681509712</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>-35.2239915315886,174.05829469594917</t>
+        </is>
+      </c>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>-35.224726284436095,174.05827605729593</t>
+        </is>
+      </c>
+      <c r="H347" t="inlineStr">
+        <is>
+          <t>-35.22545918815837,174.05832619637795</t>
+        </is>
+      </c>
+      <c r="I347" t="inlineStr">
+        <is>
+          <t>-35.22619311471177,174.05833995212663</t>
+        </is>
+      </c>
+      <c r="J347" t="inlineStr">
+        <is>
+          <t>-35.22692774647801,174.05833464503064</t>
+        </is>
+      </c>
+      <c r="K347" t="inlineStr">
+        <is>
+          <t>-35.22766164017051,174.0583510831043</t>
+        </is>
+      </c>
+      <c r="L347" t="inlineStr">
+        <is>
+          <t>-35.22839585636091,174.05842164440338</t>
+        </is>
+      </c>
+      <c r="M347" t="inlineStr">
+        <is>
+          <t>-35.22912088651775,174.05858861886878</t>
+        </is>
+      </c>
+      <c r="N347" t="inlineStr">
+        <is>
+          <t>-35.22982585324848,174.05884642050148</t>
+        </is>
+      </c>
+      <c r="O347" t="inlineStr">
+        <is>
+          <t>-35.230487309221374,174.05923161128828</t>
+        </is>
+      </c>
+      <c r="P347" t="inlineStr">
+        <is>
+          <t>-35.231108484132555,174.059711765787</t>
+        </is>
+      </c>
+      <c r="Q347" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0063/nzd0063.xlsx
+++ b/data/nzd0063/nzd0063.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q347"/>
+  <dimension ref="A1:Q350"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20231,6 +20231,177 @@
       <c r="Q347" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-01 22:10:40+00:00</t>
+        </is>
+      </c>
+      <c r="B348" t="n">
+        <v>360.16</v>
+      </c>
+      <c r="C348" t="n">
+        <v>342.25</v>
+      </c>
+      <c r="D348" t="n">
+        <v>351.39</v>
+      </c>
+      <c r="E348" t="n">
+        <v>355.02</v>
+      </c>
+      <c r="F348" t="n">
+        <v>360.6</v>
+      </c>
+      <c r="G348" t="n">
+        <v>356.83</v>
+      </c>
+      <c r="H348" t="n">
+        <v>358.77</v>
+      </c>
+      <c r="I348" t="n">
+        <v>357.25</v>
+      </c>
+      <c r="J348" t="n">
+        <v>354.63</v>
+      </c>
+      <c r="K348" t="n">
+        <v>352.6</v>
+      </c>
+      <c r="L348" t="n">
+        <v>357.67</v>
+      </c>
+      <c r="M348" t="n">
+        <v>357.96</v>
+      </c>
+      <c r="N348" t="n">
+        <v>357.28</v>
+      </c>
+      <c r="O348" t="n">
+        <v>360.76</v>
+      </c>
+      <c r="P348" t="n">
+        <v>358.18</v>
+      </c>
+      <c r="Q348" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:30+00:00</t>
+        </is>
+      </c>
+      <c r="B349" t="n">
+        <v>357.99</v>
+      </c>
+      <c r="C349" t="n">
+        <v>343.03</v>
+      </c>
+      <c r="D349" t="n">
+        <v>351.12</v>
+      </c>
+      <c r="E349" t="n">
+        <v>355.73</v>
+      </c>
+      <c r="F349" t="n">
+        <v>361.19</v>
+      </c>
+      <c r="G349" t="n">
+        <v>357.74</v>
+      </c>
+      <c r="H349" t="n">
+        <v>360.31</v>
+      </c>
+      <c r="I349" t="n">
+        <v>356.83</v>
+      </c>
+      <c r="J349" t="n">
+        <v>356.12</v>
+      </c>
+      <c r="K349" t="n">
+        <v>354.27</v>
+      </c>
+      <c r="L349" t="n">
+        <v>358.59</v>
+      </c>
+      <c r="M349" t="n">
+        <v>358.86</v>
+      </c>
+      <c r="N349" t="n">
+        <v>358.84</v>
+      </c>
+      <c r="O349" t="n">
+        <v>362.36</v>
+      </c>
+      <c r="P349" t="n">
+        <v>358.77</v>
+      </c>
+      <c r="Q349" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:11:11+00:00</t>
+        </is>
+      </c>
+      <c r="B350" t="n">
+        <v>357.6</v>
+      </c>
+      <c r="C350" t="n">
+        <v>344.34</v>
+      </c>
+      <c r="D350" t="n">
+        <v>353.07</v>
+      </c>
+      <c r="E350" t="n">
+        <v>356.55</v>
+      </c>
+      <c r="F350" t="n">
+        <v>362.17</v>
+      </c>
+      <c r="G350" t="n">
+        <v>358.8</v>
+      </c>
+      <c r="H350" t="n">
+        <v>362.11</v>
+      </c>
+      <c r="I350" t="n">
+        <v>358.12</v>
+      </c>
+      <c r="J350" t="n">
+        <v>357.49</v>
+      </c>
+      <c r="K350" t="n">
+        <v>355.36</v>
+      </c>
+      <c r="L350" t="n">
+        <v>359.57</v>
+      </c>
+      <c r="M350" t="n">
+        <v>360.4</v>
+      </c>
+      <c r="N350" t="n">
+        <v>360.01</v>
+      </c>
+      <c r="O350" t="n">
+        <v>363.75</v>
+      </c>
+      <c r="P350" t="n">
+        <v>360.04</v>
+      </c>
+      <c r="Q350" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -20245,7 +20416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B354"/>
+  <dimension ref="A1:B357"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23788,6 +23959,36 @@
       </c>
       <c r="B354" t="n">
         <v>0.13</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>2026-06-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B355" t="n">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B356" t="n">
+        <v>-0.51</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B357" t="n">
+        <v>0.86</v>
       </c>
     </row>
   </sheetData>
@@ -23956,28 +24157,28 @@
         <v>0.0544</v>
       </c>
       <c r="I2" t="n">
-        <v>0.07042009061035669</v>
+        <v>0.07420678998281945</v>
       </c>
       <c r="J2" t="n">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="K2" t="n">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01848585888114562</v>
+        <v>0.02083180662774897</v>
       </c>
       <c r="M2" t="n">
-        <v>2.971709780700763</v>
+        <v>2.96593103359104</v>
       </c>
       <c r="N2" t="n">
-        <v>14.52640117307892</v>
+        <v>14.45108447956122</v>
       </c>
       <c r="O2" t="n">
-        <v>3.811351620236437</v>
+        <v>3.801458204368584</v>
       </c>
       <c r="P2" t="n">
-        <v>354.5487447296141</v>
+        <v>354.5091334391608</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -24038,28 +24239,28 @@
         <v>0.06</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.02537842103680209</v>
+        <v>-0.02606820736994616</v>
       </c>
       <c r="J3" t="n">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="K3" t="n">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003691936252166905</v>
+        <v>0.003971906210023968</v>
       </c>
       <c r="M3" t="n">
-        <v>2.239041702640344</v>
+        <v>2.227506085318431</v>
       </c>
       <c r="N3" t="n">
-        <v>9.589072346139407</v>
+        <v>9.514319351097919</v>
       </c>
       <c r="O3" t="n">
-        <v>3.096622732290682</v>
+        <v>3.084529032299407</v>
       </c>
       <c r="P3" t="n">
-        <v>344.2789065285402</v>
+        <v>344.2861132319841</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -24120,28 +24321,28 @@
         <v>0.06279999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01072279320055061</v>
+        <v>0.01047824908299044</v>
       </c>
       <c r="J4" t="n">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="K4" t="n">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0004740232905504627</v>
+        <v>0.0004618126700624003</v>
       </c>
       <c r="M4" t="n">
-        <v>2.70928792055881</v>
+        <v>2.693400313896018</v>
       </c>
       <c r="N4" t="n">
-        <v>13.40981680557029</v>
+        <v>13.3008378468738</v>
       </c>
       <c r="O4" t="n">
-        <v>3.661941671513937</v>
+        <v>3.64703137453927</v>
       </c>
       <c r="P4" t="n">
-        <v>351.7114055078993</v>
+        <v>351.7139533289089</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -24202,28 +24403,28 @@
         <v>0.09859999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.01900255047915316</v>
+        <v>-0.02269514145472795</v>
       </c>
       <c r="J5" t="n">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="K5" t="n">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="L5" t="n">
-        <v>0.002183518530425754</v>
+        <v>0.003162089974751203</v>
       </c>
       <c r="M5" t="n">
-        <v>2.312511923157187</v>
+        <v>2.311511631975544</v>
       </c>
       <c r="N5" t="n">
-        <v>9.103859110057106</v>
+        <v>9.065648944259847</v>
       </c>
       <c r="O5" t="n">
-        <v>3.017260199263084</v>
+        <v>3.010921610447513</v>
       </c>
       <c r="P5" t="n">
-        <v>358.3719976434469</v>
+        <v>358.4106298312415</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -24284,28 +24485,28 @@
         <v>0.0949</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.06140148417112069</v>
+        <v>-0.0643985588836265</v>
       </c>
       <c r="J6" t="n">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="K6" t="n">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="L6" t="n">
-        <v>0.024930136985576</v>
+        <v>0.02781394123496805</v>
       </c>
       <c r="M6" t="n">
-        <v>2.187206578015473</v>
+        <v>2.182621267486001</v>
       </c>
       <c r="N6" t="n">
-        <v>8.135359583823673</v>
+        <v>8.093231081094242</v>
       </c>
       <c r="O6" t="n">
-        <v>2.852255175089296</v>
+        <v>2.844860467772408</v>
       </c>
       <c r="P6" t="n">
-        <v>364.6689649691924</v>
+        <v>364.7003187811756</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -24366,28 +24567,28 @@
         <v>0.1142</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.008580526888683795</v>
+        <v>-0.01717883108653936</v>
       </c>
       <c r="J7" t="n">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="K7" t="n">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0004297795127290449</v>
+        <v>0.001718649117754989</v>
       </c>
       <c r="M7" t="n">
-        <v>2.455836924871428</v>
+        <v>2.472747509346977</v>
       </c>
       <c r="N7" t="n">
-        <v>9.447207624014476</v>
+        <v>9.570524610443483</v>
       </c>
       <c r="O7" t="n">
-        <v>3.073631016243569</v>
+        <v>3.093626449725869</v>
       </c>
       <c r="P7" t="n">
-        <v>362.9023857712473</v>
+        <v>362.9923505860631</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -24448,28 +24649,28 @@
         <v>0.1166</v>
       </c>
       <c r="I8" t="n">
-        <v>0.03207247411987005</v>
+        <v>0.02772544807006677</v>
       </c>
       <c r="J8" t="n">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="K8" t="n">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="L8" t="n">
-        <v>0.005404784882720448</v>
+        <v>0.004101698083788019</v>
       </c>
       <c r="M8" t="n">
-        <v>2.532795795658154</v>
+        <v>2.532528213340065</v>
       </c>
       <c r="N8" t="n">
-        <v>10.44337387603068</v>
+        <v>10.42056425685038</v>
       </c>
       <c r="O8" t="n">
-        <v>3.231620936315192</v>
+        <v>3.228089877443065</v>
       </c>
       <c r="P8" t="n">
-        <v>362.0053373145363</v>
+        <v>362.0508077700611</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -24530,28 +24731,28 @@
         <v>0.1574</v>
       </c>
       <c r="I9" t="n">
-        <v>0.08181587567846668</v>
+        <v>0.07403666400957831</v>
       </c>
       <c r="J9" t="n">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="K9" t="n">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04383840827226215</v>
+        <v>0.03618791894982842</v>
       </c>
       <c r="M9" t="n">
-        <v>2.333905886764712</v>
+        <v>2.35019938965372</v>
       </c>
       <c r="N9" t="n">
-        <v>8.054890307771906</v>
+        <v>8.150893662349686</v>
       </c>
       <c r="O9" t="n">
-        <v>2.838113864483225</v>
+        <v>2.854976998567534</v>
       </c>
       <c r="P9" t="n">
-        <v>359.6240917875654</v>
+        <v>359.7054914153319</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -24612,28 +24813,28 @@
         <v>0.1396</v>
       </c>
       <c r="I10" t="n">
-        <v>0.07570632174227759</v>
+        <v>0.06896546192133987</v>
       </c>
       <c r="J10" t="n">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="K10" t="n">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="L10" t="n">
-        <v>0.03000110934418321</v>
+        <v>0.02520552480353921</v>
       </c>
       <c r="M10" t="n">
-        <v>2.210995641433462</v>
+        <v>2.225891668574036</v>
       </c>
       <c r="N10" t="n">
-        <v>10.2236544669827</v>
+        <v>10.26983344941572</v>
       </c>
       <c r="O10" t="n">
-        <v>3.197444990454519</v>
+        <v>3.204658086195112</v>
       </c>
       <c r="P10" t="n">
-        <v>357.8800628368305</v>
+        <v>357.9505858453839</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -24694,28 +24895,28 @@
         <v>0.1321</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.01871435980518077</v>
+        <v>-0.02561127685134056</v>
       </c>
       <c r="J11" t="n">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="K11" t="n">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="L11" t="n">
-        <v>0.001374057065297252</v>
+        <v>0.002597702952423342</v>
       </c>
       <c r="M11" t="n">
-        <v>2.867034147897305</v>
+        <v>2.885484146505354</v>
       </c>
       <c r="N11" t="n">
-        <v>14.04287311485638</v>
+        <v>14.06132106189692</v>
       </c>
       <c r="O11" t="n">
-        <v>3.747382168241768</v>
+        <v>3.749842804958218</v>
       </c>
       <c r="P11" t="n">
-        <v>358.4953310091852</v>
+        <v>358.5674875825608</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -24776,28 +24977,28 @@
         <v>0.08840000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>0.02168091588376258</v>
+        <v>0.01450274736794519</v>
       </c>
       <c r="J12" t="n">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="K12" t="n">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="L12" t="n">
-        <v>0.001766064513840204</v>
+        <v>0.0007995027503772123</v>
       </c>
       <c r="M12" t="n">
-        <v>2.958020472533059</v>
+        <v>2.964223773557962</v>
       </c>
       <c r="N12" t="n">
-        <v>14.65848077232382</v>
+        <v>14.6762813888899</v>
       </c>
       <c r="O12" t="n">
-        <v>3.828639545886217</v>
+        <v>3.830963506598556</v>
       </c>
       <c r="P12" t="n">
-        <v>362.1050056079527</v>
+        <v>362.1801100626448</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -24858,28 +25059,28 @@
         <v>0.09229999999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.03364185645718355</v>
+        <v>-0.0374056135343164</v>
       </c>
       <c r="J13" t="n">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="K13" t="n">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="L13" t="n">
-        <v>0.009095262274701477</v>
+        <v>0.01137219946975387</v>
       </c>
       <c r="M13" t="n">
-        <v>2.031080598725668</v>
+        <v>2.030953320556862</v>
       </c>
       <c r="N13" t="n">
-        <v>6.802750324491295</v>
+        <v>6.79117156395412</v>
       </c>
       <c r="O13" t="n">
-        <v>2.608208259417045</v>
+        <v>2.60598763695343</v>
       </c>
       <c r="P13" t="n">
-        <v>362.1134905332098</v>
+        <v>362.1528624033026</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -24940,28 +25141,28 @@
         <v>0.1044</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.002009729023665607</v>
+        <v>-0.008790979959426525</v>
       </c>
       <c r="J14" t="n">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="K14" t="n">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="L14" t="n">
-        <v>1.990626308767673e-05</v>
+        <v>0.0003839919803195757</v>
       </c>
       <c r="M14" t="n">
-        <v>2.39162759651615</v>
+        <v>2.409764211465938</v>
       </c>
       <c r="N14" t="n">
-        <v>11.19398114769837</v>
+        <v>11.23229277676428</v>
       </c>
       <c r="O14" t="n">
-        <v>3.345740747233469</v>
+        <v>3.351461289760673</v>
       </c>
       <c r="P14" t="n">
-        <v>362.6141576091896</v>
+        <v>362.685104003158</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -25022,28 +25223,28 @@
         <v>0.1029</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.0255671035484699</v>
+        <v>-0.03025889476713659</v>
       </c>
       <c r="J15" t="n">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="K15" t="n">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="L15" t="n">
-        <v>0.00345924866669034</v>
+        <v>0.004904322211802925</v>
       </c>
       <c r="M15" t="n">
-        <v>2.375666416086085</v>
+        <v>2.379184313432011</v>
       </c>
       <c r="N15" t="n">
-        <v>10.41571099466739</v>
+        <v>10.39824347320615</v>
       </c>
       <c r="O15" t="n">
-        <v>3.227338066374111</v>
+        <v>3.224630749900856</v>
       </c>
       <c r="P15" t="n">
-        <v>365.6401122602753</v>
+        <v>365.6891558004698</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -25104,28 +25305,28 @@
         <v>0.1246</v>
       </c>
       <c r="I16" t="n">
-        <v>0.009395789683897293</v>
+        <v>0.003722648846086701</v>
       </c>
       <c r="J16" t="n">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="K16" t="n">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0006446374221037443</v>
+        <v>0.0001020956642765469</v>
       </c>
       <c r="M16" t="n">
-        <v>2.183369303736761</v>
+        <v>2.19346247611366</v>
       </c>
       <c r="N16" t="n">
-        <v>7.56978574428642</v>
+        <v>7.596622015891981</v>
       </c>
       <c r="O16" t="n">
-        <v>2.751324361882186</v>
+        <v>2.756197020514314</v>
       </c>
       <c r="P16" t="n">
-        <v>361.9683626167589</v>
+        <v>362.0276739077214</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -25167,7 +25368,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q347"/>
+  <dimension ref="A1:Q350"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55347,6 +55548,267 @@
         </is>
       </c>
     </row>
+    <row r="348">
+      <c r="A348" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-01 22:10:40+00:00</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>-35.22121179217551,174.05925293176642</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>-35.22179613189804,174.05867144696677</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>-35.22250484761022,174.05835632382033</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>-35.223254334751566,174.0582513759889</t>
+        </is>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>-35.22399141097446,174.05826777702927</t>
+        </is>
+      </c>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>-35.2247269997961,174.05824816246928</t>
+        </is>
+      </c>
+      <c r="H348" t="inlineStr">
+        <is>
+          <t>-35.22546012416831,174.05829138412884</t>
+        </is>
+      </c>
+      <c r="I348" t="inlineStr">
+        <is>
+          <t>-35.22619435593879,174.0582993255108</t>
+        </is>
+      </c>
+      <c r="J348" t="inlineStr">
+        <is>
+          <t>-35.22692887239028,174.05830050030235</t>
+        </is>
+      </c>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>-35.22766308391518,174.0583081561749</t>
+        </is>
+      </c>
+      <c r="L348" t="inlineStr">
+        <is>
+          <t>-35.228398414622404,174.0583953473305</t>
+        </is>
+      </c>
+      <c r="M348" t="inlineStr">
+        <is>
+          <t>-35.22912536238715,174.05856733028747</t>
+        </is>
+      </c>
+      <c r="N348" t="inlineStr">
+        <is>
+          <t>-35.229831472744465,174.0588279823803</t>
+        </is>
+      </c>
+      <c r="O348" t="inlineStr">
+        <is>
+          <t>-35.230496330945414,174.05921157405152</t>
+        </is>
+      </c>
+      <c r="P348" t="inlineStr">
+        <is>
+          <t>-35.2311196224692,174.0596918954981</t>
+        </is>
+      </c>
+      <c r="Q348" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:30+00:00</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>-35.22120311153597,174.05923156496326</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>-35.22179922257788,174.05867914498</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>-35.22250413140807,174.05835348855123</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>-35.22325494098878,174.05825914196615</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>-35.22399144002086,174.0582742595447</t>
+        </is>
+      </c>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>-35.22472674350646,174.0582581562852</t>
+        </is>
+      </c>
+      <c r="H349" t="inlineStr">
+        <is>
+          <t>-35.22545966945179,174.0583082960733</t>
+        </is>
+      </c>
+      <c r="I349" t="inlineStr">
+        <is>
+          <t>-35.226194496833976,174.05829471384078</t>
+        </is>
+      </c>
+      <c r="J349" t="inlineStr">
+        <is>
+          <t>-35.22692833296727,174.05831685903087</t>
+        </is>
+      </c>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>-35.227662467279295,174.05832649069487</t>
+        </is>
+      </c>
+      <c r="L349" t="inlineStr">
+        <is>
+          <t>-35.22839743802533,174.05840538604735</t>
+        </is>
+      </c>
+      <c r="M349" t="inlineStr">
+        <is>
+          <t>-35.229123348246375,174.05857691014936</t>
+        </is>
+      </c>
+      <c r="N349" t="inlineStr">
+        <is>
+          <t>-35.229826575306795,174.0588440513576</t>
+        </is>
+      </c>
+      <c r="O349" t="inlineStr">
+        <is>
+          <t>-35.230489391157974,174.05922698731098</t>
+        </is>
+      </c>
+      <c r="P349" t="inlineStr">
+        <is>
+          <t>-35.23111662173041,174.0596972486815</t>
+        </is>
+      </c>
+      <c r="Q349" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:11:11+00:00</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>-35.22120155142061,174.05922772484703</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>-35.22180441333392,174.05869207369577</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>-35.222509303977546,174.05837396549603</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>-35.22325564114945,174.05826811112306</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>-35.22399148826667,174.05828502711262</t>
+        </is>
+      </c>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>-35.2247264449702,174.05826979743333</t>
+        </is>
+      </c>
+      <c r="H350" t="inlineStr">
+        <is>
+          <t>-35.22545913796197,174.05832806328087</t>
+        </is>
+      </c>
+      <c r="I350" t="inlineStr">
+        <is>
+          <t>-35.22619406408395,174.05830887825573</t>
+        </is>
+      </c>
+      <c r="J350" t="inlineStr">
+        <is>
+          <t>-35.22692783698579,174.05833190027764</t>
+        </is>
+      </c>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>-35.22766206480287,174.05833845753705</t>
+        </is>
+      </c>
+      <c r="L350" t="inlineStr">
+        <is>
+          <t>-35.228396397736226,174.0584160794628</t>
+        </is>
+      </c>
+      <c r="M350" t="inlineStr">
+        <is>
+          <t>-35.22911990182598,174.05859330235634</t>
+        </is>
+      </c>
+      <c r="N350" t="inlineStr">
+        <is>
+          <t>-35.229822902227134,174.05885610308923</t>
+        </is>
+      </c>
+      <c r="O350" t="inlineStr">
+        <is>
+          <t>-35.23048336221609,174.05924037757796</t>
+        </is>
+      </c>
+      <c r="P350" t="inlineStr">
+        <is>
+          <t>-35.23111016251226,174.05970877163423</t>
+        </is>
+      </c>
+      <c r="Q350" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
